--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6296296296296297</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="B2">
-        <v>0.1785714285714286</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6267605633802817</v>
+        <v>0.5633802816901409</v>
       </c>
       <c r="D2">
-        <v>0.4862385321100918</v>
+        <v>0.512396694214876</v>
       </c>
       <c r="E2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6781609195402298</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5633802816901409</v>
+        <v>0.5492957746478874</v>
       </c>
       <c r="D2">
-        <v>0.512396694214876</v>
+        <v>0.5245901639344263</v>
       </c>
       <c r="E2">
         <v>87</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
